--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484356_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484356_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5302</v>
+        <v>7.1142</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9896</v>
+        <v>5.3829</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5406</v>
+        <v>1.7313</v>
       </c>
       <c r="G2" t="n">
         <v>6.8485</v>
@@ -610,13 +610,13 @@
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3692</v>
+        <v>-0.0469</v>
       </c>
       <c r="T2" t="n">
-        <v>0.864</v>
+        <v>0.2573</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4948</v>
+        <v>-0.3042</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6642</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2019</v>
+        <v>6.4702</v>
       </c>
       <c r="E3" t="n">
-        <v>5.497</v>
+        <v>5.9014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7049</v>
+        <v>0.5687</v>
       </c>
       <c r="G3" t="n">
         <v>5.8773</v>
@@ -688,13 +688,13 @@
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8475</v>
+        <v>-0.5792</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5447</v>
+        <v>-0.1402</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3028</v>
+        <v>-0.439</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8425</v>
+        <v>4.1809</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6547</v>
+        <v>4.8569</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8121</v>
+        <v>-0.676</v>
       </c>
       <c r="G4" t="n">
         <v>4.0475</v>
@@ -766,13 +766,13 @@
         <v>2.5395</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3455</v>
+        <v>-1.0071</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.341</v>
+        <v>-0.1388</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0045</v>
+        <v>-0.8683</v>
       </c>
       <c r="V4" t="n">
         <v>0.5545</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7859</v>
+        <v>2.887</v>
       </c>
       <c r="E5" t="n">
-        <v>3.321</v>
+        <v>3.4221</v>
       </c>
       <c r="F5" t="n">
         <v>-0.5351</v>
@@ -844,10 +844,10 @@
         <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0456</v>
+        <v>-0.9445</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.22</v>
+        <v>-0.1189</v>
       </c>
       <c r="U5" t="n">
         <v>-0.8256</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1442</v>
+        <v>1.3897</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5758</v>
+        <v>0.7669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5684</v>
+        <v>0.6228</v>
       </c>
       <c r="G6" t="n">
         <v>0.8086</v>
@@ -922,13 +922,13 @@
         <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2221</v>
+        <v>0.4677</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1666</v>
+        <v>0.3577</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0555</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2772</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4531</v>
+        <v>0.5075</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2398</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6929</v>
+        <v>0.7473</v>
       </c>
       <c r="G7" t="n">
         <v>0.2667</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0285</v>
+        <v>-0.974</v>
       </c>
       <c r="T7" t="n">
         <v>-0.4237</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6048</v>
+        <v>-0.5503</v>
       </c>
       <c r="V7" t="n">
         <v>1.6056</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1824</v>
+        <v>0.2563</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.406</v>
+        <v>-0.3048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5884</v>
+        <v>0.5612</v>
       </c>
       <c r="G8" t="n">
         <v>-0.225</v>
@@ -1078,13 +1078,13 @@
         <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3153</v>
+        <v>-0.2415</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1943</v>
+        <v>-0.2215</v>
       </c>
       <c r="V8" t="n">
         <v>0.3321</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0175</v>
+        <v>0.0992</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0201</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0376</v>
+        <v>0.1193</v>
       </c>
       <c r="G9" t="n">
         <v>0.3751</v>
@@ -1156,13 +1156,13 @@
         <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2757</v>
+        <v>-0.194</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2152</v>
+        <v>-0.1335</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3715</v>
+        <v>-0.2629</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2726</v>
+        <v>-1.5648</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9011</v>
+        <v>1.3019</v>
       </c>
       <c r="G10" t="n">
         <v>0.5259</v>
@@ -1234,13 +1234,13 @@
         <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.518</v>
+        <v>-0.4094</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1362</v>
+        <v>-0.4284</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6182</v>
+        <v>0.019</v>
       </c>
       <c r="V10" t="n">
         <v>2.16</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.739</v>
+        <v>-0.3305</v>
       </c>
       <c r="E11" t="n">
         <v>0.4827</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2218</v>
+        <v>-0.8133</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0702</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8446</v>
+        <v>-0.4361</v>
       </c>
       <c r="T11" t="n">
         <v>-0.0989</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7457</v>
+        <v>-0.3372</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9962</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0138</v>
+        <v>-1.2783</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6158</v>
+        <v>0.5147</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6297</v>
+        <v>-1.7931</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6449</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2404</v>
+        <v>-0.0241</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3247</v>
+        <v>0.2236</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0843</v>
+        <v>-0.2477</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6093</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.0334</v>
+        <v>21.0333</v>
       </c>
       <c r="E13" t="n">
         <v>19.1981</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8352</v>
+        <v>1.835</v>
       </c>
       <c r="G13" t="n">
         <v>19.2037</v>
@@ -1468,7 +1468,7 @@
         <v>12.6973</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.388999999999999</v>
+        <v>-4.389099999999999</v>
       </c>
       <c r="T13" t="n">
         <v>-0.5907</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5563</v>
+        <v>4.2124</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0127</v>
+        <v>5.3161</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4564</v>
+        <v>-1.1037</v>
       </c>
       <c r="G14" t="n">
         <v>1.1779</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0463</v>
+        <v>0.7024</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3744</v>
+        <v>0.6778</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3281</v>
+        <v>0.0246</v>
       </c>
       <c r="V14" t="n">
         <v>1.5507</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.538</v>
+        <v>0.5878</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5322</v>
+        <v>2.4199</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9942</v>
+        <v>-1.8321</v>
       </c>
       <c r="G15" t="n">
         <v>0.4404</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2028</v>
+        <v>1.2526</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8161</v>
+        <v>0.7038</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3867</v>
+        <v>0.5488</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4959</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6304</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.762</v>
+        <v>0.1979</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3924</v>
+        <v>-1.0119</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9345</v>
+        <v>-1.0809</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3282</v>
+        <v>-0.4467</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.2627</v>
+        <v>-0.6342</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8623</v>
+        <v>0.1428</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2361</v>
+        <v>0.1023</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3739</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7967</v>
+        <v>-1.2237</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9079</v>
+        <v>-0.549</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8889</v>
+        <v>-0.6747</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6947</v>
+        <v>-0.1238</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8299</v>
+        <v>0.0551</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8648</v>
+        <v>-0.1789</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2729</v>
+        <v>-1.5691</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2066</v>
+        <v>-0.148</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0663</v>
+        <v>-1.421</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0809</v>
+        <v>-0.9345</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4467</v>
+        <v>2.3282</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6342</v>
+        <v>-3.2627</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1428</v>
+        <v>1.8623</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1023</v>
+        <v>3.2361</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-1.3739</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2237</v>
+        <v>-2.7967</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.549</v>
+        <v>-0.9079</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6747</v>
+        <v>-1.8889</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5827</v>
+        <v>1.7561</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3494</v>
+        <v>0.9198</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2333</v>
+        <v>0.8363</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9854</v>
+        <v>-3.2846</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3368</v>
+        <v>-0.4721</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3223</v>
+        <v>-2.8125</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7197</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2264</v>
+        <v>0.9273</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5794</v>
+        <v>0.7705</v>
       </c>
       <c r="U18" t="n">
-        <v>0.647</v>
+        <v>0.1567</v>
       </c>
       <c r="V18" t="n">
         <v>-2.4921</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.0211</v>
+        <v>-4.6119</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0259</v>
+        <v>-1.2277</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9951</v>
+        <v>-3.3842</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5793</v>
+        <v>-4.9484</v>
       </c>
       <c r="H19" t="n">
-        <v>0.372</v>
+        <v>-3.0602</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.9512</v>
+        <v>-1.8883</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5129</v>
+        <v>-1.4073</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0888</v>
+        <v>-1.4083</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6016</v>
+        <v>0.001</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0664</v>
+        <v>-3.5411</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7168</v>
+        <v>-1.6518</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3496</v>
+        <v>-1.8893</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6372</v>
+        <v>0.45</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1457</v>
+        <v>0.6372</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4915</v>
+        <v>-0.1872</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6093</v>
+        <v>1.4959</v>
       </c>
       <c r="X19" t="n">
         <v>-1.2186</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0865</v>
+        <v>-4.745</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.43</v>
+        <v>-0.7226</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6565</v>
+        <v>-4.0224</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.9484</v>
+        <v>-3.5793</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.0602</v>
+        <v>0.372</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8883</v>
+        <v>-3.9512</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4073</v>
+        <v>-0.5129</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4083</v>
+        <v>2.0888</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001</v>
+        <v>-2.6016</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5411</v>
+        <v>-3.0664</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6518</v>
+        <v>-1.7168</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8893</v>
+        <v>-1.3496</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0246</v>
+        <v>-0.361</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4349</v>
+        <v>0.1577</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4596</v>
+        <v>-0.5187</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="X20" t="n">
         <v>-1.2186</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7381</v>
+        <v>-4.8294</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2009</v>
+        <v>-2.2909</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5372</v>
+        <v>-2.5386</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2291</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.509</v>
+        <v>0.3997</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9546</v>
+        <v>-0.0446</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4456</v>
+        <v>0.4442</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2186</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3932</v>
+        <v>-5.3054</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6155</v>
+        <v>-4.9077</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.3978</v>
       </c>
       <c r="G22" t="n">
         <v>-5.33</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0278</v>
+        <v>0.0599</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.241</v>
+        <v>0.1389</v>
       </c>
       <c r="V22" t="n">
         <v>0.9414</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-21.0333</v>
+        <v>-20.3592</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.835199999999999</v>
+        <v>-1.835100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-19.1981</v>
+        <v>-18.5242</v>
       </c>
       <c r="G23" t="n">
         <v>-19.2036</v>
@@ -2233,7 +2233,7 @@
         <v>-22.4989</v>
       </c>
       <c r="N23" t="n">
-        <v>-9.680100000000001</v>
+        <v>-9.680099999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-12.8188</v>
@@ -2248,13 +2248,13 @@
         <v>10.7439</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3889</v>
+        <v>5.063199999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>3.7982</v>
+        <v>3.7983</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5905999999999999</v>
+        <v>1.2647</v>
       </c>
       <c r="V23" t="n">
         <v>-4.2652</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484356_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484356_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PINEÑO JIMENEZ</t>
+          <t>J. PINENO JIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2563</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3048</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5612</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.225</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0361</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1889</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2849</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3083</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0599</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3443</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2415</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0199</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2215</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0992</v>
+        <v>0.2563</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0201</v>
+        <v>-0.3048</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1193</v>
+        <v>0.5612</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3751</v>
+        <v>-0.225</v>
       </c>
       <c r="H9" t="n">
-        <v>0.065</v>
+        <v>-0.0361</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3101</v>
+        <v>-0.1889</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0405</v>
+        <v>-0.2849</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.3083</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3346</v>
+        <v>0.0599</v>
       </c>
       <c r="N9" t="n">
-        <v>0.065</v>
+        <v>-0.3443</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2696</v>
+        <v>0.4043</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.194</v>
+        <v>-0.2415</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0605</v>
+        <v>-0.0199</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1335</v>
+        <v>-0.2215</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1234,72 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2629</v>
+        <v>0.0992</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5648</v>
+        <v>-0.0201</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3019</v>
+        <v>0.1193</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5259</v>
+        <v>0.3751</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.756</v>
+        <v>0.065</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2819</v>
+        <v>0.3101</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3099</v>
+        <v>0.0405</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7009</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.609</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.784</v>
+        <v>0.3346</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4569</v>
+        <v>0.065</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.2696</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4094</v>
+        <v>-0.194</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4284</v>
+        <v>-0.0605</v>
       </c>
       <c r="U10" t="n">
-        <v>0.019</v>
+        <v>-0.1335</v>
       </c>
       <c r="V10" t="n">
-        <v>2.16</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,11 +1379,16 @@
       <c r="X11" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2783</v>
+        <v>-0.5699</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5147</v>
+        <v>-1.8718</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7931</v>
+        <v>1.3019</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6449</v>
+        <v>0.2189</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.307</v>
+        <v>-1.0629</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3379</v>
+        <v>1.2819</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2678</v>
+        <v>1.0029</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0655</v>
+        <v>0.3939</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2023</v>
+        <v>0.609</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9127</v>
+        <v>-0.784</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3725</v>
+        <v>-1.4569</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5403</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-4.8836</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>2.3441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0241</v>
+        <v>-0.4094</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2236</v>
+        <v>-0.4284</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2477</v>
+        <v>0.019</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6093</v>
+        <v>2.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.0333</v>
+        <v>-1.2783</v>
       </c>
       <c r="E13" t="n">
-        <v>19.1981</v>
+        <v>0.5147</v>
       </c>
       <c r="F13" t="n">
-        <v>1.835</v>
+        <v>-1.7931</v>
       </c>
       <c r="G13" t="n">
-        <v>19.2037</v>
+        <v>-0.6449</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3248000000000001</v>
+        <v>-0.307</v>
       </c>
       <c r="I13" t="n">
-        <v>18.8788</v>
+        <v>-0.3379</v>
       </c>
       <c r="J13" t="n">
-        <v>22.499</v>
+        <v>1.2678</v>
       </c>
       <c r="K13" t="n">
-        <v>9.680199999999999</v>
+        <v>1.0655</v>
       </c>
       <c r="L13" t="n">
-        <v>12.8188</v>
+        <v>0.2023</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2953</v>
+        <v>-1.9127</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.355399999999999</v>
+        <v>-1.3725</v>
       </c>
       <c r="O13" t="n">
-        <v>6.06</v>
+        <v>-0.5403</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.7438</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>12.6973</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.389099999999999</v>
+        <v>-0.0241</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5907</v>
+        <v>0.2236</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.7983</v>
+        <v>-0.2477</v>
       </c>
       <c r="V13" t="n">
-        <v>4.2654</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>8.033799999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7684</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2124</v>
+        <v>21.0333</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3161</v>
+        <v>19.1981</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1037</v>
+        <v>1.835</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1779</v>
+        <v>19.2037</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4019</v>
+        <v>0.3249000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.224</v>
+        <v>18.8788</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1192</v>
+        <v>22.499</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9936</v>
+        <v>9.680199999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8745000000000001</v>
+        <v>12.8188</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.9413</v>
+        <v>-3.2953</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5917</v>
+        <v>-9.355399999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3496</v>
+        <v>6.06</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-10.7438</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>12.6973</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7024</v>
+        <v>-4.3891</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6778</v>
+        <v>-0.5907</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0246</v>
+        <v>-3.7983</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5507</v>
+        <v>4.2654</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>8.033799999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0549</v>
-      </c>
+        <v>-3.7684</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5878</v>
+        <v>4.2124</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4199</v>
+        <v>5.3161</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8321</v>
+        <v>-1.1037</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4404</v>
+        <v>1.1779</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4242</v>
+        <v>3.4019</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9838</v>
+        <v>-2.224</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6928</v>
+        <v>4.1192</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1924</v>
+        <v>4.9936</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5004</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2524</v>
+        <v>-2.9413</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7682</v>
+        <v>-1.5917</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4842</v>
+        <v>-1.3496</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2526</v>
+        <v>0.7024</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7038</v>
+        <v>0.6778</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5488</v>
+        <v>0.0246</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4959</v>
+        <v>1.5507</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1728,72 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.5878</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1979</v>
+        <v>2.4199</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0119</v>
+        <v>-1.8321</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0809</v>
+        <v>0.4404</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4467</v>
+        <v>1.4242</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6342</v>
+        <v>-0.9838</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1428</v>
+        <v>2.6928</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1023</v>
+        <v>2.1924</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>0.5004</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2237</v>
+        <v>-2.2524</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.549</v>
+        <v>-0.7682</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6747</v>
+        <v>-1.4842</v>
       </c>
       <c r="P16" t="n">
         <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1238</v>
+        <v>1.2526</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0551</v>
+        <v>0.7038</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1789</v>
+        <v>0.5488</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5691</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.148</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.421</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9345</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3282</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.2627</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8623</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2361</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3739</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7967</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9079</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8889</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7561</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9198</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8363</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2846</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4721</v>
+        <v>0.1979</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8125</v>
+        <v>-1.0119</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7197</v>
+        <v>-1.0809</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6273</v>
+        <v>-0.4467</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.347</v>
+        <v>-0.6342</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4531</v>
+        <v>0.1428</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0463</v>
+        <v>0.1023</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1729</v>
+        <v>-1.2237</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.419</v>
+        <v>-0.549</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7538</v>
+        <v>-0.6747</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9273</v>
+        <v>-0.1238</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7705</v>
+        <v>0.0551</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1567</v>
+        <v>-0.1789</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4921</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.6119</v>
+        <v>-1.8761</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2277</v>
+        <v>-0.455</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3842</v>
+        <v>-1.421</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9484</v>
+        <v>-1.2415</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.0602</v>
+        <v>2.0213</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8883</v>
+        <v>-3.2627</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4073</v>
+        <v>1.5553</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4083</v>
+        <v>2.9291</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001</v>
+        <v>-1.3739</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5411</v>
+        <v>-2.7967</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6518</v>
+        <v>-0.9079</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8893</v>
+        <v>-1.8889</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.45</v>
+        <v>1.7561</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6372</v>
+        <v>0.9198</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1872</v>
+        <v>0.8363</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.745</v>
+        <v>-3.2846</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7226</v>
+        <v>-0.4721</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0224</v>
+        <v>-2.8125</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5793</v>
+        <v>-1.7197</v>
       </c>
       <c r="H20" t="n">
-        <v>0.372</v>
+        <v>0.6273</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.9512</v>
+        <v>-2.347</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5129</v>
+        <v>0.4531</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0888</v>
+        <v>1.0463</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6016</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0664</v>
+        <v>-2.1729</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7168</v>
+        <v>-0.419</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3496</v>
+        <v>-1.7538</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.361</v>
+        <v>0.9273</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1577</v>
+        <v>0.7705</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5187</v>
+        <v>0.1567</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>-2.4921</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6093</v>
+        <v>-0.719</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8294</v>
+        <v>-4.6119</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2909</v>
+        <v>-1.2277</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5386</v>
+        <v>-3.3842</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2291</v>
+        <v>-4.9484</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.2285</v>
+        <v>-3.0602</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.8883</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9022</v>
+        <v>-1.4073</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7115</v>
+        <v>-1.4083</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8093</v>
+        <v>0.001</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3269</v>
+        <v>-3.5411</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.517</v>
+        <v>-1.6518</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8099</v>
+        <v>-1.8893</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3997</v>
+        <v>0.45</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0446</v>
+        <v>0.6372</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4442</v>
+        <v>-0.1872</v>
       </c>
       <c r="V21" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X21" t="n">
         <v>-1.2186</v>
       </c>
-      <c r="W21" t="n">
-        <v>0.6093</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-1.8279</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3054</v>
+        <v>-4.745</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9077</v>
+        <v>-0.7226</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3978</v>
+        <v>-4.0224</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.33</v>
+        <v>-3.5793</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7432</v>
+        <v>0.372</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.5868</v>
+        <v>-3.9512</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.1525</v>
+        <v>-0.5129</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1845</v>
+        <v>2.0888</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.968</v>
+        <v>-2.6016</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1775</v>
+        <v>-3.0664</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5587</v>
+        <v>-1.7168</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6188</v>
+        <v>-1.3496</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0599</v>
+        <v>-0.361</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.079</v>
+        <v>0.1577</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1389</v>
+        <v>-0.5187</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9414</v>
+        <v>-0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-4.8294</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.2909</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.5386</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3.2291</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3.2285</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.9022</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.7115</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.8093</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.3269</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.517</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.8099</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L. ANDUJAR MASCARO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5.3054</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.9077</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.3978</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.7432</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.5868</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.1525</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.1845</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.968</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.1775</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.6188</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.079</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484356_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-20.3592</v>
       </c>
-      <c r="E23" t="n">
-        <v>-1.835100000000001</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E25" t="n">
+        <v>-1.8351</v>
+      </c>
+      <c r="F25" t="n">
         <v>-18.5242</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>-19.2036</v>
       </c>
-      <c r="H23" t="n">
-        <v>-0.3250000000000004</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H25" t="n">
+        <v>-0.3249000000000002</v>
+      </c>
+      <c r="I25" t="n">
         <v>-18.8786</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>3.2953</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>9.3552</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>-6.06</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>-22.4989</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-9.680099999999999</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-12.8188</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>10.7439</v>
       </c>
-      <c r="S23" t="n">
-        <v>5.063199999999999</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="S25" t="n">
+        <v>5.0632</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.7983</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>1.2647</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V25" t="n">
         <v>-4.2652</v>
       </c>
-      <c r="W23" t="n">
-        <v>3.7686</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-8.033600000000002</v>
-      </c>
+      <c r="W25" t="n">
+        <v>3.768600000000001</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-8.0336</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
